--- a/app/src/main/assets/methodmesh/odk_templates/sms/example_odk_sms_send.xlsx
+++ b/app/src/main/assets/methodmesh/odk_templates/sms/example_odk_sms_send.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="Rfa0e7b3756f045e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="Rd278eeb0122443e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="R1396c27fb8d04823"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="R0b917ee0e07247a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="Rf9447222ddfe4ff7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="R6f5a6021a45a4b1e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -12,136 +12,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
-    <x:t xml:space="preserve">type</x:t>
+    <x:t xml:space="preserve">list_name</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">name</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">label</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">calculation</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">appearance</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">body::intent</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">readonly</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">start</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Start time</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">text</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">phone_number</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Phone number</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">field_value</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Value to include in SMS</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">calculate</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sms_message_calc</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SMS message</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">concat('Your study code is ', ${field_value}, '.')</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">begin_group</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">send_sms</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">field-list</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">note</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sms_preview</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Message to send: ${sms_message}</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">true()</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sms_phone</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SMS phone</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sms_message</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sms_message_sha256</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SMS message SHA-256</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sms_status</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SMS status</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">integer</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sms_parts</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SMS parts</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sms_sent_time_iso</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SMS sent time</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sms_error</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SMS error</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">end_group</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">end_send_sms</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">end</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">End time</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">list_name</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -418,106 +295,127 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B1" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C1" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D1" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E1" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F1" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G1" t="s">
-        <x:v>6</x:v>
+      <x:c r="A1" t="str">
+        <x:v>type</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>name</x:v>
+      </x:c>
+      <x:c r="C1" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="D1" t="str">
+        <x:v>calculation</x:v>
+      </x:c>
+      <x:c r="E1" t="str">
+        <x:v>appearance</x:v>
+      </x:c>
+      <x:c r="F1" t="str">
+        <x:v>body::intent</x:v>
+      </x:c>
+      <x:c r="G1" t="str">
+        <x:v>readonly</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B2" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C2" t="s">
-        <x:v>8</x:v>
-      </x:c>
+      <x:c r="A2" t="str">
+        <x:v>start</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>start</x:v>
+      </x:c>
+      <x:c r="C2" t="str">
+        <x:v>Start time</x:v>
+      </x:c>
+      <x:c r="D2"/>
+      <x:c r="E2"/>
+      <x:c r="F2"/>
+      <x:c r="G2"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B3" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C3" t="s">
-        <x:v>11</x:v>
-      </x:c>
+      <x:c r="A3" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>phone_number</x:v>
+      </x:c>
+      <x:c r="C3" t="str">
+        <x:v>Phone numbers (comma, semicolon, or newline separated)</x:v>
+      </x:c>
+      <x:c r="D3"/>
+      <x:c r="E3"/>
+      <x:c r="F3"/>
+      <x:c r="G3"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B4" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C4" t="s">
-        <x:v>13</x:v>
-      </x:c>
+      <x:c r="A4" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>field_value</x:v>
+      </x:c>
+      <x:c r="C4" t="str">
+        <x:v>Value to include in SMS</x:v>
+      </x:c>
+      <x:c r="D4"/>
+      <x:c r="E4"/>
+      <x:c r="F4"/>
+      <x:c r="G4"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B5" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C5" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D5" t="s">
-        <x:v>17</x:v>
-      </x:c>
+      <x:c r="A5" t="str">
+        <x:v>calculate</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>sms_message_calc</x:v>
+      </x:c>
+      <x:c r="C5" t="str">
+        <x:v>SMS message</x:v>
+      </x:c>
+      <x:c r="D5" t="str">
+        <x:v>concat('Your study code is ', ${field_value}, '.')</x:v>
+      </x:c>
+      <x:c r="E5"/>
+      <x:c r="F5"/>
+      <x:c r="G5"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B6" t="s">
-        <x:v>19</x:v>
+      <x:c r="A6" t="str">
+        <x:v>begin_group</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>send_sms</x:v>
       </x:c>
       <x:c r="C6" t="str">
         <x:v>Send SMS through MethodMesh</x:v>
       </x:c>
-      <x:c r="E6" t="s">
-        <x:v>20</x:v>
+      <x:c r="D6"/>
+      <x:c r="E6" t="str">
+        <x:v>field-list</x:v>
       </x:c>
       <x:c r="F6" t="str">
         <x:v>com.example.methodmesh.EXECUTE_METHOD(method_id='sms.send',input_sms_phone=${phone_number},input_sms_message=${sms_message_calc},return_mode='flat')</x:v>
       </x:c>
+      <x:c r="G6"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="B7" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C7" t="s">
-        <x:v>23</x:v>
-      </x:c>
+      <x:c r="A7" t="str">
+        <x:v>note</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>sms_preview</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>Message to send: ${sms_message}</x:v>
+      </x:c>
+      <x:c r="D7"/>
+      <x:c r="E7"/>
+      <x:c r="F7"/>
+      <x:c r="G7"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" t="s">
-        <x:v>9</x:v>
+      <x:c r="A8" t="str">
+        <x:v>text</x:v>
       </x:c>
       <x:c r="B8" t="str">
         <x:v>methodmesh_execution_id</x:v>
@@ -525,13 +423,16 @@
       <x:c r="C8" t="str">
         <x:v>MethodMesh execution ID</x:v>
       </x:c>
-      <x:c r="G8" t="s">
-        <x:v>24</x:v>
+      <x:c r="D8"/>
+      <x:c r="E8"/>
+      <x:c r="F8"/>
+      <x:c r="G8" t="str">
+        <x:v>true()</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" t="s">
-        <x:v>9</x:v>
+      <x:c r="A9" t="str">
+        <x:v>text</x:v>
       </x:c>
       <x:c r="B9" t="str">
         <x:v>methodmesh_status</x:v>
@@ -539,126 +440,210 @@
       <x:c r="C9" t="str">
         <x:v>MethodMesh status</x:v>
       </x:c>
-      <x:c r="G9" t="s">
-        <x:v>24</x:v>
+      <x:c r="D9"/>
+      <x:c r="E9"/>
+      <x:c r="F9"/>
+      <x:c r="G9" t="str">
+        <x:v>true()</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B10" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C10" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G10" t="s">
-        <x:v>24</x:v>
+      <x:c r="A10" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>sms_phone</x:v>
+      </x:c>
+      <x:c r="C10" t="str">
+        <x:v>SMS phone</x:v>
+      </x:c>
+      <x:c r="D10"/>
+      <x:c r="E10"/>
+      <x:c r="F10"/>
+      <x:c r="G10" t="str">
+        <x:v>true()</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B11" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G11" t="s">
-        <x:v>24</x:v>
+      <x:c r="A11" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>sms_message</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>SMS message</x:v>
+      </x:c>
+      <x:c r="D11"/>
+      <x:c r="E11"/>
+      <x:c r="F11"/>
+      <x:c r="G11" t="str">
+        <x:v>true()</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B12" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C12" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="G12" t="s">
-        <x:v>24</x:v>
+      <x:c r="A12" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>sms_message_sha256</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>SMS message SHA-256</x:v>
+      </x:c>
+      <x:c r="D12"/>
+      <x:c r="E12"/>
+      <x:c r="F12"/>
+      <x:c r="G12" t="str">
+        <x:v>true()</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B13" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C13" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G13" t="s">
-        <x:v>24</x:v>
+      <x:c r="A13" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>sms_status</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>SMS status</x:v>
+      </x:c>
+      <x:c r="D13"/>
+      <x:c r="E13"/>
+      <x:c r="F13"/>
+      <x:c r="G13" t="str">
+        <x:v>true()</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="B14" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C14" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="G14" t="s">
-        <x:v>24</x:v>
+      <x:c r="A14" t="str">
+        <x:v>integer</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>sms_parts</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>SMS parts</x:v>
+      </x:c>
+      <x:c r="D14"/>
+      <x:c r="E14"/>
+      <x:c r="F14"/>
+      <x:c r="G14" t="str">
+        <x:v>true()</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B15" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C15" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="G15" t="s">
-        <x:v>24</x:v>
+      <x:c r="A15" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>sms_sent_time_iso</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>SMS sent time</x:v>
+      </x:c>
+      <x:c r="D15"/>
+      <x:c r="E15"/>
+      <x:c r="F15"/>
+      <x:c r="G15" t="str">
+        <x:v>true()</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B16" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C16" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="G16" t="s">
-        <x:v>24</x:v>
+      <x:c r="A16" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>sms_error</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>SMS error</x:v>
+      </x:c>
+      <x:c r="D16"/>
+      <x:c r="E16"/>
+      <x:c r="F16"/>
+      <x:c r="G16" t="str">
+        <x:v>true()</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="B17" t="s">
-        <x:v>40</x:v>
-      </x:c>
+      <x:c r="A17" t="str">
+        <x:v>end_group</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>end_send_sms</x:v>
+      </x:c>
+      <x:c r="C17"/>
+      <x:c r="D17"/>
+      <x:c r="E17"/>
+      <x:c r="F17"/>
+      <x:c r="G17"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="B18" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C18" t="s">
-        <x:v>42</x:v>
-      </x:c>
+      <x:c r="A18" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>sms_recipients_json</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>SMS recipients JSON</x:v>
+      </x:c>
+      <x:c r="D18"/>
+      <x:c r="E18"/>
+      <x:c r="F18"/>
+      <x:c r="G18" t="str">
+        <x:v>true()</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>integer</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>sms_recipient_count</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>SMS recipient count</x:v>
+      </x:c>
+      <x:c r="D19"/>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
+      <x:c r="G19" t="str">
+        <x:v>true()</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>sms_recipient_results_json</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>SMS recipient results JSON</x:v>
+      </x:c>
+      <x:c r="D20"/>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
+      <x:c r="G20" t="str">
+        <x:v>true()</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>end</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>end</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>End time</x:v>
+      </x:c>
+      <x:c r="D21"/>
+      <x:c r="E21"/>
+      <x:c r="F21"/>
+      <x:c r="G21"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -674,7 +659,7 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" t="s">
-        <x:v>43</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B1" t="s">
         <x:v>1</x:v>
@@ -720,7 +705,7 @@
         <x:v>example_odk_sms_send</x:v>
       </x:c>
       <x:c r="C2" t="str">
-        <x:v>2026090703</x:v>
+        <x:v>2026101602</x:v>
       </x:c>
       <x:c r="D2" t="str">
         <x:v>concat('sms.send - ', ${field_value})</x:v>
